--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -454,23 +454,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>16.79895</v>
+        <v>16.44341</v>
       </c>
       <c r="D2" t="n">
-        <v>16.81832</v>
+        <v>16.81714</v>
       </c>
       <c r="E2" t="n">
-        <v>16.85823</v>
+        <v>16.78276</v>
       </c>
       <c r="F2" t="n">
-        <v>42.50559</v>
+        <v>42.60488</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05052</v>
+        <v>0.05113</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8579</v>
+        <v>1.86051</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90303</v>
+        <v>16.95991</v>
       </c>
       <c r="D3" t="n">
-        <v>16.32454</v>
+        <v>16.4135</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55043</v>
+        <v>16.81815</v>
       </c>
       <c r="F3" t="n">
-        <v>42.60633</v>
+        <v>4221.142</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05044</v>
+        <v>0.05063</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82794</v>
+        <v>1.88407</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.33915</v>
+        <v>16.72558</v>
       </c>
       <c r="D4" t="n">
-        <v>16.46025</v>
+        <v>16.34044</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70137</v>
+        <v>16.55856</v>
       </c>
       <c r="F4" t="n">
-        <v>42.35901</v>
+        <v>42.62203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05023</v>
+        <v>0.04964</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77789</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.06461</v>
+        <v>16.96395</v>
       </c>
       <c r="D5" t="n">
-        <v>16.68836</v>
+        <v>16.38119</v>
       </c>
       <c r="E5" t="n">
-        <v>16.823</v>
+        <v>16.55751</v>
       </c>
       <c r="F5" t="n">
-        <v>41.72761</v>
+        <v>41.60197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05075</v>
+        <v>0.05111</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7939</v>
+        <v>1.88009</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.9046</v>
+        <v>16.98381</v>
       </c>
       <c r="D6" t="n">
-        <v>16.97214</v>
+        <v>16.38239</v>
       </c>
       <c r="E6" t="n">
-        <v>16.60756</v>
+        <v>16.58313</v>
       </c>
       <c r="F6" t="n">
-        <v>41.45488</v>
+        <v>42.1986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05079</v>
+        <v>0.05009</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80769</v>
+        <v>1.80754</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81796</v>
+        <v>17.03659</v>
       </c>
       <c r="D7" t="n">
-        <v>16.58026</v>
+        <v>16.76143</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76956</v>
+        <v>16.76587</v>
       </c>
       <c r="F7" t="n">
-        <v>41.77614</v>
+        <v>42.51727</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05074</v>
+        <v>0.04956</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80737</v>
+        <v>1.78975</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.98121</v>
+        <v>16.74607</v>
       </c>
       <c r="D8" t="n">
-        <v>16.60238</v>
+        <v>16.51718</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67215</v>
+        <v>16.72815</v>
       </c>
       <c r="F8" t="n">
-        <v>42.40715</v>
+        <v>42.19543</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05152</v>
+        <v>0.05158</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85353</v>
+        <v>1.7977</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.49053</v>
+        <v>16.88356</v>
       </c>
       <c r="D9" t="n">
-        <v>16.64337</v>
+        <v>16.69795</v>
       </c>
       <c r="E9" t="n">
-        <v>16.64336</v>
+        <v>16.8676</v>
       </c>
       <c r="F9" t="n">
-        <v>42.8532</v>
+        <v>42.79971</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04962</v>
+        <v>0.051</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79683</v>
+        <v>1.82473</v>
       </c>
     </row>
     <row r="10">
@@ -655,51 +660,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.18642</v>
+        <v>16.91511</v>
       </c>
       <c r="D10" t="n">
-        <v>16.5029</v>
+        <v>16.59641</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71029</v>
+        <v>16.7658</v>
       </c>
       <c r="F10" t="n">
-        <v>43.18124</v>
+        <v>42.43879</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0504</v>
+        <v>0.05081</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8344</v>
+        <v>1.85525</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -713,26 +698,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.77355</v>
+        <v>0.59511</v>
       </c>
       <c r="D12" t="n">
-        <v>16.68105</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.49811</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.1596</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.04998</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.80394</v>
+        <v>1.13495</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.73802</v>
+        <v>0.61258</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4872</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.57737</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41.18656</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05034</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.77114</v>
+        <v>1.12507</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.01805</v>
+        <v>0.61866</v>
       </c>
       <c r="D14" t="n">
-        <v>16.88394</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.9624</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.4058</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05132</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.80855</v>
+        <v>1.11568</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.44886</v>
+        <v>0.61591</v>
       </c>
       <c r="D15" t="n">
-        <v>16.25451</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.68557</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.19814</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.04987</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.82593</v>
+        <v>1.10545</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.67435</v>
+        <v>0.60187</v>
       </c>
       <c r="D16" t="n">
-        <v>16.81356</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.8591</v>
-      </c>
-      <c r="F16" t="n">
-        <v>41.57747</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05085</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.8055</v>
+        <v>1.12408</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.73396</v>
+        <v>0.6111</v>
       </c>
       <c r="D17" t="n">
-        <v>16.73874</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.80824</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43.04967</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.04971</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.83973</v>
+        <v>1.11881</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.52374</v>
+        <v>0.60638</v>
       </c>
       <c r="D18" t="n">
-        <v>16.52589</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.42088</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.51447</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05023</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.79651</v>
+        <v>1.11428</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.73317</v>
+        <v>0.61071</v>
       </c>
       <c r="D19" t="n">
-        <v>16.52265</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.50317</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43.50924</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05114</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.80159</v>
+        <v>1.12286</v>
       </c>
     </row>
     <row r="20">
@@ -917,22 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.11405</v>
+        <v>0.60668</v>
       </c>
       <c r="D20" t="n">
-        <v>16.63101</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.36517</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.91132</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05038</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.80057</v>
+        <v>1.1463</v>
       </c>
     </row>
     <row r="21">
@@ -989,28 +866,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.73878</v>
+        <v>0.73472</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08032</v>
+        <v>0.08265</v>
       </c>
       <c r="E22" t="n">
-        <v>0.61359</v>
+        <v>0.60089</v>
       </c>
       <c r="F22" t="n">
-        <v>0.98456</v>
+        <v>0.96421</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1093</v>
+        <v>0.10903</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00771</v>
+        <v>0.00767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09281</v>
+        <v>0.09336</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12781</v>
+        <v>0.12678</v>
       </c>
     </row>
     <row r="23">
@@ -1020,28 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75557</v>
+        <v>0.73255</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08099000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.60689</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95849</v>
+        <v>0.96857</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10852</v>
+        <v>0.10786</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00762</v>
+        <v>0.00769</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09191000000000001</v>
+        <v>0.09157999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12899</v>
+        <v>0.12772</v>
       </c>
     </row>
     <row r="24">
@@ -1051,28 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.73913</v>
+        <v>0.75761</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08321000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61958</v>
+        <v>0.61175</v>
       </c>
       <c r="F24" t="n">
-        <v>0.93843</v>
+        <v>0.98042</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11004</v>
+        <v>0.1082</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00749</v>
+        <v>0.00765</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09225</v>
+        <v>0.09207</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1249</v>
+        <v>0.1258</v>
       </c>
     </row>
     <row r="25">
@@ -1082,28 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7390600000000001</v>
+        <v>0.75074</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07921</v>
+        <v>0.0825</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61163</v>
+        <v>0.60142</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9557</v>
+        <v>0.96107</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10849</v>
+        <v>0.11049</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0077</v>
+        <v>0.00759</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09725</v>
+        <v>0.09293999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1262</v>
+        <v>0.12496</v>
       </c>
     </row>
     <row r="26">
@@ -1113,28 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.76315</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08112</v>
+        <v>0.08263</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60034</v>
+        <v>0.59939</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97175</v>
+        <v>0.97322</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10933</v>
+        <v>0.11016</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00755</v>
+        <v>0.00766</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09359000000000001</v>
+        <v>0.09293</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12576</v>
+        <v>0.12625</v>
       </c>
     </row>
     <row r="27">
@@ -1144,28 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74797</v>
+        <v>0.74121</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07965</v>
+        <v>0.08058</v>
       </c>
       <c r="E27" t="n">
-        <v>0.61886</v>
+        <v>0.62121</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9686</v>
+        <v>0.97443</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11069</v>
+        <v>0.10792</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00764</v>
+        <v>0.00762</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09288</v>
+        <v>0.09331</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12737</v>
+        <v>0.12712</v>
       </c>
     </row>
     <row r="28">
@@ -1175,28 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74541</v>
+        <v>0.74272</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08046</v>
+        <v>0.08094</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6091800000000001</v>
+        <v>0.60038</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9531500000000001</v>
+        <v>0.97822</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10864</v>
+        <v>0.11063</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00768</v>
+        <v>0.00742</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09104</v>
+        <v>0.09143</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12494</v>
+        <v>0.12557</v>
       </c>
     </row>
     <row r="29">
@@ -1206,28 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74442</v>
+        <v>0.75374</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08037</v>
+        <v>0.08104</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62631</v>
+        <v>0.61372</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95674</v>
+        <v>0.9598</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10844</v>
+        <v>0.10891</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00753</v>
+        <v>0.00764</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09318</v>
+        <v>0.09354999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12631</v>
+        <v>0.12396</v>
       </c>
     </row>
     <row r="30">
@@ -1237,28 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74622</v>
+        <v>0.7471</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08176</v>
+        <v>0.08387</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60601</v>
+        <v>0.60987</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96595</v>
+        <v>0.9867</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10754</v>
+        <v>0.10773</v>
       </c>
       <c r="H30" t="n">
         <v>0.00768</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09132999999999999</v>
+        <v>0.0944</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12961</v>
+        <v>0.12725</v>
       </c>
     </row>
   </sheetData>
